--- a/tame_output/ON/bt/strategyON_20240628.xlsx
+++ b/tame_output/ON/bt/strategyON_20240628.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.8%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.2%</t>
+          <t>451.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-522.0%</t>
+          <t>-522.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.4%</t>
+          <t>-163.7%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-211.5%</t>
+          <t>-211.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-74.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2007"/>
+  <dimension ref="A1:G2008"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.716502642086473</v>
+        <v>3.714941193321643</v>
       </c>
       <c r="C2007" t="n">
         <v>3.569771103756472</v>
@@ -47722,6 +47722,29 @@
       </c>
       <c r="G2007" t="n">
         <v>3.720699544010835</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" s="2" t="n">
+        <v>45470</v>
+      </c>
+      <c r="B2008" t="n">
+        <v>3.72847766797952</v>
+      </c>
+      <c r="C2008" t="n">
+        <v>3.567882916650247</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>-3.605447943523816</v>
+      </c>
+      <c r="E2008" t="n">
+        <v>2.125347314926973</v>
+      </c>
+      <c r="F2008" t="n">
+        <v>0.2515474004239375</v>
+      </c>
+      <c r="G2008" t="n">
+        <v>3.71881135690461</v>
       </c>
     </row>
   </sheetData>
